--- a/data/trans_orig/P13_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25503</t>
+          <t>26359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49355</t>
+          <t>51850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442285</t>
+          <t>441693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461780</t>
+          <t>461226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281177</t>
+          <t>280321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297056</t>
+          <t>297412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>731102</t>
+          <t>728607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>754648</t>
+          <t>753903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354219</t>
+          <t>354376</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365341</t>
+          <t>365301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353909</t>
+          <t>355163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367650</t>
+          <t>367743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>714873</t>
+          <t>715431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731288</t>
+          <t>731478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18341</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33824</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524048</t>
+          <t>524756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537341</t>
+          <t>537346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145968</t>
+          <t>145733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161468</t>
+          <t>161365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676347</t>
+          <t>676478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>695753</t>
+          <t>695712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60169</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48551</t>
+          <t>47917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64433</t>
+          <t>63047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100052</t>
+          <t>97914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1178165</t>
+          <t>1178907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1205190</t>
+          <t>1204563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665734</t>
+          <t>666368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689567</t>
+          <t>689689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1852568</t>
+          <t>1854706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1888187</t>
+          <t>1889573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33791</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28528</t>
+          <t>28239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53835</t>
+          <t>53375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324914</t>
+          <t>323933</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>340257</t>
+          <t>340476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>534961</t>
+          <t>535409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>554591</t>
+          <t>554021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>865472</t>
+          <t>865932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890779</t>
+          <t>891068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>53027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86747</t>
+          <t>86530</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60356</t>
+          <t>60620</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96808</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282972</t>
+          <t>283306</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295200</t>
+          <t>295161</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1162013</t>
+          <t>1162230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1195059</t>
+          <t>1195733</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1450152</t>
+          <t>1453037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1486604</t>
+          <t>1486340</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86145</t>
+          <t>84314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125758</t>
+          <t>127878</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138413</t>
+          <t>139325</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>191500</t>
+          <t>191573</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>237065</t>
+          <t>236663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300964</t>
+          <t>301408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3144432</t>
+          <t>3142312</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3184045</t>
+          <t>3185876</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3186624</t>
+          <t>3186551</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3239711</t>
+          <t>3238799</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6347350</t>
+          <t>6346906</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6411249</t>
+          <t>6411651</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>28227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>39793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409890</t>
+          <t>408037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426991</t>
+          <t>426823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294265</t>
+          <t>295038</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307674</t>
+          <t>308264</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>710342</t>
+          <t>710925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>732214</t>
+          <t>731266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>28295</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>32090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26498</t>
+          <t>26494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52912</t>
+          <t>52286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390531</t>
+          <t>390502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408708</t>
+          <t>408637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>305839</t>
+          <t>305921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326671</t>
+          <t>326163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703896</t>
+          <t>704522</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730310</t>
+          <t>730314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48825</t>
+          <t>47457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33922</t>
+          <t>34732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43931</t>
+          <t>43528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74538</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>580590</t>
+          <t>581958</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>605967</t>
+          <t>605877</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226207</t>
+          <t>225397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244279</t>
+          <t>244710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>815006</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>845613</t>
+          <t>846016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>45098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76568</t>
+          <t>77115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44242</t>
+          <t>44792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75298</t>
+          <t>75965</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>96709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140418</t>
+          <t>142095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1080446</t>
+          <t>1079899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1112767</t>
+          <t>1111916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689405</t>
+          <t>688738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720461</t>
+          <t>719911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1781299</t>
+          <t>1779622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1823443</t>
+          <t>1825008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28736</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77608</t>
+          <t>76538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116543</t>
+          <t>115394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93134</t>
+          <t>93453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135173</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>481860</t>
+          <t>481846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498388</t>
+          <t>498706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>644979</t>
+          <t>646128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>683914</t>
+          <t>684984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1136945</t>
+          <t>1137989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1178984</t>
+          <t>1178665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100528</t>
+          <t>101774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147564</t>
+          <t>145358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110679</t>
+          <t>110552</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156723</t>
+          <t>155869</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245942</t>
+          <t>245284</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260531</t>
+          <t>260287</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>960690</t>
+          <t>962896</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1007726</t>
+          <t>1006480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1218413</t>
+          <t>1219267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1264457</t>
+          <t>1264584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135340</t>
+          <t>133317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187889</t>
+          <t>184393</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>296101</t>
+          <t>298251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>368479</t>
+          <t>365354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>447897</t>
+          <t>447291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>533501</t>
+          <t>534516</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3231078</t>
+          <t>3234574</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3283627</t>
+          <t>3285650</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3178594</t>
+          <t>3181719</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3250972</t>
+          <t>3248822</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6432539</t>
+          <t>6431524</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6518143</t>
+          <t>6518749</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>25008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402482</t>
+          <t>403111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418985</t>
+          <t>419840</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320871</t>
+          <t>320557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336829</t>
+          <t>337252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730344</t>
+          <t>730956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>752919</t>
+          <t>753762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>15643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30202</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358840</t>
+          <t>357818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371310</t>
+          <t>371292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356606</t>
+          <t>356630</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368890</t>
+          <t>368976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>719298</t>
+          <t>720064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>737388</t>
+          <t>738055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>32402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23482</t>
+          <t>24566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25775</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>49567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>488011</t>
+          <t>489512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508380</t>
+          <t>509475</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142641</t>
+          <t>141557</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157664</t>
+          <t>157213</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>637426</t>
+          <t>638469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662261</t>
+          <t>662714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26420</t>
+          <t>26861</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53259</t>
+          <t>54571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68490</t>
+          <t>67901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71200</t>
+          <t>70754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110783</t>
+          <t>111322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1096379</t>
+          <t>1095067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1123218</t>
+          <t>1122777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>755486</t>
+          <t>756075</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>785491</t>
+          <t>785587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1862832</t>
+          <t>1862293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1902415</t>
+          <t>1902861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41765</t>
+          <t>41346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35081</t>
+          <t>35014</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62943</t>
+          <t>62098</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62419</t>
+          <t>61043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98930</t>
+          <t>94441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>578941</t>
+          <t>579360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>599592</t>
+          <t>600947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>675301</t>
+          <t>676146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>703163</t>
+          <t>703230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1260020</t>
+          <t>1264509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1296531</t>
+          <t>1297907</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44049</t>
+          <t>45284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76040</t>
+          <t>76005</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46413</t>
+          <t>47080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79474</t>
+          <t>78563</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280501</t>
+          <t>280866</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1004714</t>
+          <t>1004749</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1036705</t>
+          <t>1035470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1288425</t>
+          <t>1289336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1321486</t>
+          <t>1320819</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97255</t>
+          <t>97605</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141572</t>
+          <t>141694</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167192</t>
+          <t>167917</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223406</t>
+          <t>225040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>277629</t>
+          <t>277983</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>350725</t>
+          <t>348591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3243177</t>
+          <t>3243055</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3287494</t>
+          <t>3287144</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3303151</t>
+          <t>3301517</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3359365</t>
+          <t>3358640</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6560582</t>
+          <t>6562716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6633678</t>
+          <t>6633324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33591</t>
+          <t>34954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>24178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30461</t>
+          <t>29994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>52046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471621</t>
+          <t>470258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490340</t>
+          <t>490090</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424022</t>
+          <t>423289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>436414</t>
+          <t>435992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>899034</t>
+          <t>900633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>922218</t>
+          <t>922685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23564</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45406</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428649</t>
+          <t>428352</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442640</t>
+          <t>442617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357884</t>
+          <t>357740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371550</t>
+          <t>371140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>789387</t>
+          <t>790011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810625</t>
+          <t>810037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39669</t>
+          <t>40950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25781</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64008</t>
+          <t>64188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627590</t>
+          <t>626309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659351</t>
+          <t>659865</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140705</t>
+          <t>141560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153538</t>
+          <t>153319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>769737</t>
+          <t>769557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817696</t>
+          <t>818825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53094</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81849</t>
+          <t>82722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24202</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66857</t>
+          <t>68203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82302</t>
+          <t>78887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138094</t>
+          <t>136666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>952970</t>
+          <t>952097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>981725</t>
+          <t>983545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>911237</t>
+          <t>909891</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>953892</t>
+          <t>951984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874818</t>
+          <t>1876246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1930610</t>
+          <t>1934025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48855</t>
+          <t>47645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55774</t>
+          <t>53695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90309</t>
+          <t>88571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89261</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129665</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424290</t>
+          <t>425500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447950</t>
+          <t>448546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>749133</t>
+          <t>750871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>783668</t>
+          <t>785747</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1182922</t>
+          <t>1182483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1223326</t>
+          <t>1225122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55677</t>
+          <t>57165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80220</t>
+          <t>82538</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59666</t>
+          <t>60266</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86088</t>
+          <t>86464</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231390</t>
+          <t>230627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238837</t>
+          <t>238941</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>678898</t>
+          <t>676580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>703441</t>
+          <t>701953</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>913538</t>
+          <t>913162</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>939960</t>
+          <t>939360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129053</t>
+          <t>127502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>194249</t>
+          <t>195970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>196109</t>
+          <t>198312</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>270554</t>
+          <t>271434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>349026</t>
+          <t>353231</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>456159</t>
+          <t>454240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3178906</t>
+          <t>3177185</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3244102</t>
+          <t>3245653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3302634</t>
+          <t>3301754</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3377079</t>
+          <t>3374876</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6490184</t>
+          <t>6492103</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6597317</t>
+          <t>6593112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32083</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>25655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>25897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51850</t>
+          <t>51945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441693</t>
+          <t>443464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461226</t>
+          <t>461013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280321</t>
+          <t>281025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297412</t>
+          <t>296767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>728607</t>
+          <t>728512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753903</t>
+          <t>754560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23368</t>
+          <t>23255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354376</t>
+          <t>353419</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365301</t>
+          <t>365344</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355163</t>
+          <t>354313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367743</t>
+          <t>367860</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>715431</t>
+          <t>715544</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731478</t>
+          <t>731099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>34176</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524756</t>
+          <t>524257</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537346</t>
+          <t>537590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145733</t>
+          <t>147223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161365</t>
+          <t>161340</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676478</t>
+          <t>675995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>695712</t>
+          <t>695756</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33771</t>
+          <t>32754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>59502</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>23713</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47917</t>
+          <t>48114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63047</t>
+          <t>62772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97914</t>
+          <t>99806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1178907</t>
+          <t>1178832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1204563</t>
+          <t>1205580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666368</t>
+          <t>666171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689689</t>
+          <t>690572</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1854706</t>
+          <t>1852814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1889573</t>
+          <t>1889848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26622</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>32514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28239</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53375</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323933</t>
+          <t>323751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>340476</t>
+          <t>340544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>535409</t>
+          <t>536238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>554021</t>
+          <t>554994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>865932</t>
+          <t>865493</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>891068</t>
+          <t>891131</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14895</t>
+          <t>15355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53027</t>
+          <t>53156</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86530</t>
+          <t>85293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60620</t>
+          <t>60720</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93923</t>
+          <t>93548</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283306</t>
+          <t>282846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295161</t>
+          <t>295025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1162230</t>
+          <t>1163467</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1195733</t>
+          <t>1195604</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1453037</t>
+          <t>1453412</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1486340</t>
+          <t>1486240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84314</t>
+          <t>84508</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127878</t>
+          <t>125005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139325</t>
+          <t>140398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>191573</t>
+          <t>192601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>236663</t>
+          <t>237248</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>301408</t>
+          <t>301847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3142312</t>
+          <t>3145185</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3185876</t>
+          <t>3185682</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3186551</t>
+          <t>3185523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3238799</t>
+          <t>3237726</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6346906</t>
+          <t>6346467</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6411651</t>
+          <t>6411066</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>17934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39793</t>
+          <t>40746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408037</t>
+          <t>410628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426823</t>
+          <t>427346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295038</t>
+          <t>293421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308264</t>
+          <t>307567</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>710925</t>
+          <t>709972</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731266</t>
+          <t>732784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28295</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26494</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52286</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390502</t>
+          <t>391648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408637</t>
+          <t>408454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>305921</t>
+          <t>306913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326163</t>
+          <t>326231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704522</t>
+          <t>704626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730314</t>
+          <t>730843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47457</t>
+          <t>48507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34732</t>
+          <t>35078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43528</t>
+          <t>43081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73317</t>
+          <t>74839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>581958</t>
+          <t>580908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>605877</t>
+          <t>606008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>225397</t>
+          <t>225051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244710</t>
+          <t>244811</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>814705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>846016</t>
+          <t>846463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>45727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77115</t>
+          <t>76819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44792</t>
+          <t>44595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75965</t>
+          <t>75872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96709</t>
+          <t>96977</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142095</t>
+          <t>142867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1079899</t>
+          <t>1080195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1111916</t>
+          <t>1111287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>688738</t>
+          <t>688831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719911</t>
+          <t>720108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1779622</t>
+          <t>1778850</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1825008</t>
+          <t>1824740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76538</t>
+          <t>75548</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115394</t>
+          <t>112025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93453</t>
+          <t>93267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134129</t>
+          <t>136552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>481846</t>
+          <t>480921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498706</t>
+          <t>498413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>646128</t>
+          <t>649497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>684984</t>
+          <t>685974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1137989</t>
+          <t>1135566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1178665</t>
+          <t>1178851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>101774</t>
+          <t>102326</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145358</t>
+          <t>145174</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110552</t>
+          <t>113514</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155869</t>
+          <t>159893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245284</t>
+          <t>245408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260287</t>
+          <t>260720</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>962896</t>
+          <t>963080</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1006480</t>
+          <t>1005928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1219267</t>
+          <t>1215243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1264584</t>
+          <t>1261622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133317</t>
+          <t>134874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184393</t>
+          <t>186879</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>298251</t>
+          <t>296357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>365354</t>
+          <t>367316</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>447291</t>
+          <t>445447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>534516</t>
+          <t>533301</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3234574</t>
+          <t>3232088</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3285650</t>
+          <t>3284093</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3181719</t>
+          <t>3179757</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3248822</t>
+          <t>3250716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6431524</t>
+          <t>6432739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6518749</t>
+          <t>6520593</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403111</t>
+          <t>403477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419840</t>
+          <t>419883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320557</t>
+          <t>320206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337252</t>
+          <t>336959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730956</t>
+          <t>730581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753762</t>
+          <t>753561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29436</t>
+          <t>29467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357818</t>
+          <t>357764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371292</t>
+          <t>371212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356630</t>
+          <t>356183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368976</t>
+          <t>369045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720064</t>
+          <t>720033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>738055</t>
+          <t>737036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32402</t>
+          <t>33290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49567</t>
+          <t>49849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>489512</t>
+          <t>488624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509475</t>
+          <t>508496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141557</t>
+          <t>141424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157213</t>
+          <t>158139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638469</t>
+          <t>638187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662714</t>
+          <t>662965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26861</t>
+          <t>26573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54571</t>
+          <t>51250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>37991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67901</t>
+          <t>66331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70754</t>
+          <t>70976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111322</t>
+          <t>110878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1095067</t>
+          <t>1098388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1122777</t>
+          <t>1123065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>756075</t>
+          <t>757645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>785587</t>
+          <t>785985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1862293</t>
+          <t>1862737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1902861</t>
+          <t>1902639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>21231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41346</t>
+          <t>40416</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35014</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62098</t>
+          <t>62492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>61301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94441</t>
+          <t>96276</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>579360</t>
+          <t>580290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>600947</t>
+          <t>599475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>676146</t>
+          <t>675752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>703489</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1264509</t>
+          <t>1262674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1297907</t>
+          <t>1297649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45284</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76005</t>
+          <t>76547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47080</t>
+          <t>46562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78563</t>
+          <t>81196</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280866</t>
+          <t>281384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1004749</t>
+          <t>1004207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1035470</t>
+          <t>1036261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1289336</t>
+          <t>1286703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1320819</t>
+          <t>1321337</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97605</t>
+          <t>97874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141694</t>
+          <t>143900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167917</t>
+          <t>167876</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>225040</t>
+          <t>225127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>277983</t>
+          <t>279448</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>348591</t>
+          <t>354622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3243055</t>
+          <t>3240849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3287144</t>
+          <t>3286875</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3301517</t>
+          <t>3301430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3358640</t>
+          <t>3358681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6562716</t>
+          <t>6556685</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6633324</t>
+          <t>6631859</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>24335</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34954</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24178</t>
+          <t>27672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>44327</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29994</t>
+          <t>33098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52046</t>
+          <t>57757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>482148</t>
+          <t>526283</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>470258</t>
+          <t>513899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490090</t>
+          <t>534775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>430347</t>
+          <t>468419</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423289</t>
+          <t>460739</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>435992</t>
+          <t>475198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>912496</t>
+          <t>994702</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>900633</t>
+          <t>981272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>922685</t>
+          <t>1005931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23861</t>
+          <t>25130</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32538</t>
+          <t>34804</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24756</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44782</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>436632</t>
+          <t>467159</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428352</t>
+          <t>458082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442617</t>
+          <t>473489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,17 +9124,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>365623</t>
+          <t>404393</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357740</t>
+          <t>395344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371140</t>
+          <t>410875</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>802255</t>
+          <t>871551</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>790011</t>
+          <t>859821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810037</t>
+          <t>880821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>25378</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40950</t>
+          <t>39076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24926</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>60076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>644707</t>
+          <t>445299</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626309</t>
+          <t>431601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659865</t>
+          <t>453869</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>148287</t>
+          <t>167276</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141560</t>
+          <t>159401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153319</t>
+          <t>173224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>792994</t>
+          <t>612575</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>769557</t>
+          <t>597619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>818825</t>
+          <t>623221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166486</t>
+          <t>187018</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166486</t>
+          <t>187018</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166486</t>
+          <t>187018</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833745</t>
+          <t>657695</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833745</t>
+          <t>657695</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833745</t>
+          <t>657695</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65623</t>
+          <t>74718</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82722</t>
+          <t>95223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48608</t>
+          <t>53873</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>42689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68203</t>
+          <t>66894</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>114231</t>
+          <t>128592</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78887</t>
+          <t>109211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136666</t>
+          <t>152610</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>969196</t>
+          <t>1057125</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>952097</t>
+          <t>1036620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>983545</t>
+          <t>1072412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>929486</t>
+          <t>807338</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>909891</t>
+          <t>794317</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>951984</t>
+          <t>818522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1898681</t>
+          <t>1864462</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1876246</t>
+          <t>1840444</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1934025</t>
+          <t>1883843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>36888</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>26553</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>49945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>74468</t>
+          <t>83394</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53695</t>
+          <t>71292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88571</t>
+          <t>97970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,27 +10075,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>109442</t>
+          <t>120283</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87465</t>
+          <t>102837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>138273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>438171</t>
+          <t>529004</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425500</t>
+          <t>515947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>448546</t>
+          <t>539339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>764974</t>
+          <t>745435</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>750871</t>
+          <t>730859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>785747</t>
+          <t>757537</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,22 +10188,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1203145</t>
+          <t>1274439</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1182483</t>
+          <t>1256449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1225122</t>
+          <t>1291885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473145</t>
+          <t>565892</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473145</t>
+          <t>565892</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473145</t>
+          <t>565892</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>839442</t>
+          <t>828829</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>839442</t>
+          <t>828829</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>839442</t>
+          <t>828829</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312587</t>
+          <t>1394722</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312587</t>
+          <t>1394722</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312587</t>
+          <t>1394722</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>67982</t>
+          <t>74231</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57165</t>
+          <t>62538</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82538</t>
+          <t>88749</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>72174</t>
+          <t>78592</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>65482</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86464</t>
+          <t>94262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236315</t>
+          <t>232867</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230627</t>
+          <t>227285</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238941</t>
+          <t>235322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>691136</t>
+          <t>767647</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>676580</t>
+          <t>753129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>701953</t>
+          <t>779340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>927452</t>
+          <t>1000513</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>913162</t>
+          <t>984843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>939360</t>
+          <t>1013623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759118</t>
+          <t>841878</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759118</t>
+          <t>841878</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759118</t>
+          <t>841878</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999626</t>
+          <t>1079105</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999626</t>
+          <t>1079105</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999626</t>
+          <t>1079105</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>165986</t>
+          <t>181734</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127502</t>
+          <t>158249</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195970</t>
+          <t>211511</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>243334</t>
+          <t>269983</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198312</t>
+          <t>245232</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>271434</t>
+          <t>296886</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>409320</t>
+          <t>451717</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>353231</t>
+          <t>416065</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>454240</t>
+          <t>484412</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3207169</t>
+          <t>3257737</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3177185</t>
+          <t>3227960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3245653</t>
+          <t>3281222</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3329854</t>
+          <t>3360507</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3301754</t>
+          <t>3333604</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3374876</t>
+          <t>3385258</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6537023</t>
+          <t>6618244</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6492103</t>
+          <t>6585549</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6593112</t>
+          <t>6653896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373155</t>
+          <t>3439471</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373155</t>
+          <t>3439471</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373155</t>
+          <t>3439471</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573188</t>
+          <t>3630490</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573188</t>
+          <t>3630490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573188</t>
+          <t>3630490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6946343</t>
+          <t>7069961</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6946343</t>
+          <t>7069961</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6946343</t>
+          <t>7069961</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
